--- a/05_quality_assessment/qa_results.xlsx
+++ b/05_quality_assessment/qa_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -137,21 +137,6 @@
   </si>
   <si>
     <t>S28</t>
-  </si>
-  <si>
-    <t>S29</t>
-  </si>
-  <si>
-    <t>S30</t>
-  </si>
-  <si>
-    <t>S31</t>
-  </si>
-  <si>
-    <t>S32</t>
-  </si>
-  <si>
-    <t>S33</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1112,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>11</v>
@@ -1147,8 +1132,8 @@
       <c r="I23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>12</v>
+      <c r="J23" s="2">
+        <v>46149.0</v>
       </c>
     </row>
     <row r="24">
@@ -1159,7 +1144,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>11</v>
@@ -1179,8 +1164,8 @@
       <c r="I24" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J24" s="2">
-        <v>46149.0</v>
+      <c r="J24" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -1255,7 +1240,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>11</v>
@@ -1275,8 +1260,8 @@
       <c r="I27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J27" s="2">
-        <v>46149.0</v>
+      <c r="J27" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -1319,7 +1304,7 @@
         <v>11</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>11</v>
@@ -1339,167 +1324,7 @@
       <c r="I29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J34" s="2">
+      <c r="J29" s="2">
         <v>46149.0</v>
       </c>
     </row>
